--- a/Hệ thống CRM/Tickets (gwt.ticket).xlsx
+++ b/Hệ thống CRM/Tickets (gwt.ticket).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="459">
   <si>
     <t>Create time</t>
   </si>
@@ -44,6 +44,15 @@
   </si>
   <si>
     <t>Ticket type</t>
+  </si>
+  <si>
+    <t>Customer/Phone</t>
+  </si>
+  <si>
+    <t>Customer/Contact/Phone</t>
+  </si>
+  <si>
+    <t>Ticket type/Last Modified on</t>
   </si>
   <si>
     <t>Kim Anh</t>
@@ -74,6 +83,9 @@
     <t>Khác</t>
   </si>
   <si>
+    <t>0905988844</t>
+  </si>
+  <si>
     <t>Chị Ngọc Anh</t>
   </si>
   <si>
@@ -98,6 +110,9 @@
     <t>Máy có mùi sau một thời gian sử dụng</t>
   </si>
   <si>
+    <t>0855016789</t>
+  </si>
+  <si>
     <t>Bùi Xuân Hải</t>
   </si>
   <si>
@@ -107,7 +122,7 @@
     <t>Kiểm tra thấy màn hình 2 cột trắng xoá không thao tác được, rút điện ra cắm lại màn cả 2 cột trở lại bình thường, nhờ khách hàng theo dõi thêm.</t>
   </si>
   <si>
-    <t xml:space="preserve">[GTE-30A01-G] Giải pháp lọc tổng đầu nguồn GE 30A </t>
+    <t xml:space="preserve">[WH30A] Giải pháp lọc tổng đầu nguồn GE 30A </t>
   </si>
   <si>
     <t>Hà Tĩnh (VN)</t>
@@ -125,6 +140,9 @@
     <t>Yêu cầu bảo hành</t>
   </si>
   <si>
+    <t xml:space="preserve">0705951947 </t>
+  </si>
+  <si>
     <t>Anh Hào</t>
   </si>
   <si>
@@ -140,6 +158,9 @@
     <t>GWT-260037</t>
   </si>
   <si>
+    <t>0898892456</t>
+  </si>
+  <si>
     <t>Anh Khoa (Liêu Hà Trinh)/ Tân</t>
   </si>
   <si>
@@ -152,6 +173,9 @@
     <t>Màn hình bấm không phản hồi. (POE)</t>
   </si>
   <si>
+    <t>0935282799</t>
+  </si>
+  <si>
     <t>Nguyen thi thu ninh</t>
   </si>
   <si>
@@ -170,6 +194,9 @@
     <t>Yêu cầu thay lõi lọc</t>
   </si>
   <si>
+    <t>0937508669</t>
+  </si>
+  <si>
     <t>Dòng nước chảy chậm, tia nước bắn tung toé</t>
   </si>
   <si>
@@ -182,7 +209,7 @@
     <t>Nguyen Hai</t>
   </si>
   <si>
-    <t>Đã gọi lại cho khách thì không thấy hiện tượng rò nước nữa, báo khách bật lại chức năng làm lạnh và theo dõi thêm.</t>
+    <t>Kỹ thuật đã gọi để hướng dẫn khách rút điện ra, lau khô nước dưới đáy máy. tắt chế độ làm lạnh đi</t>
   </si>
   <si>
     <t>[CTS20NG] Máy lọc nước GE CTS20NG</t>
@@ -197,6 +224,9 @@
     <t>GWT-260033</t>
   </si>
   <si>
+    <t>0908380179</t>
+  </si>
+  <si>
     <t>Phạm Huyền Trang</t>
   </si>
   <si>
@@ -215,6 +245,9 @@
     <t>GWT-260032</t>
   </si>
   <si>
+    <t>0981813888</t>
+  </si>
+  <si>
     <t>Nguyễn Trung Kiên</t>
   </si>
   <si>
@@ -227,6 +260,9 @@
     <t>GWT-260031</t>
   </si>
   <si>
+    <t>0903113128</t>
+  </si>
+  <si>
     <t>Châu Thị Yến Ly</t>
   </si>
   <si>
@@ -242,13 +278,10 @@
     <t>GWT-260030</t>
   </si>
   <si>
+    <t>0976052126</t>
+  </si>
+  <si>
     <t>Anh Cường (Long Biên)</t>
-  </si>
-  <si>
-    <t>[GTEF-30A02-G] Thiết bị lọc nước trung tâm GE (GTEF-30A02-G)</t>
-  </si>
-  <si>
-    <t>F00000212AV7S00040006</t>
   </si>
   <si>
     <t>GWT-260029</t>
@@ -274,6 +307,9 @@
     <t>GWT-260028</t>
   </si>
   <si>
+    <t>0983017886</t>
+  </si>
+  <si>
     <t>Hoàng Thị Vân Anh</t>
   </si>
   <si>
@@ -295,6 +331,9 @@
     <t>Yêu cầu bảo trì</t>
   </si>
   <si>
+    <t>0943866456</t>
+  </si>
+  <si>
     <t>Khách phát hiện khoang đổ muối không có nước, nhìn vào màn hình thấy màn hình làm mềm bị sọc</t>
   </si>
   <si>
@@ -307,6 +346,9 @@
     <t>GWT-260025</t>
   </si>
   <si>
+    <t>9375086669</t>
+  </si>
+  <si>
     <t>Nguyễn Mộc Lan</t>
   </si>
   <si>
@@ -322,6 +364,9 @@
     <t>GWT-260024</t>
   </si>
   <si>
+    <t>0898125566</t>
+  </si>
+  <si>
     <t>Anh Tú</t>
   </si>
   <si>
@@ -337,6 +382,9 @@
     <t>GWT-260022</t>
   </si>
   <si>
+    <t>0915343237</t>
+  </si>
+  <si>
     <t>Chị My</t>
   </si>
   <si>
@@ -352,6 +400,9 @@
     <t>hỏng bơm</t>
   </si>
   <si>
+    <t>0937886882</t>
+  </si>
+  <si>
     <t>Kngoc</t>
   </si>
   <si>
@@ -382,6 +433,9 @@
     <t>GWT-260019</t>
   </si>
   <si>
+    <t>0768957628</t>
+  </si>
+  <si>
     <t>Chị Phương</t>
   </si>
   <si>
@@ -395,6 +449,9 @@
   </si>
   <si>
     <t>GWT-260018</t>
+  </si>
+  <si>
+    <t>0867731688</t>
   </si>
   <si>
     <t>Vy Vy</t>
@@ -442,6 +499,9 @@
     <t>GWT-260015</t>
   </si>
   <si>
+    <t>0912371970</t>
+  </si>
+  <si>
     <t>Sự cố mất nước POE</t>
   </si>
   <si>
@@ -455,17 +515,19 @@
     <t>Hoàng Khánh Linh</t>
   </si>
   <si>
-    <t xml:space="preserve"> Làm mềm bị lỗi, cảm biến muối ko báo , main đơ dẫn đến việc chu trình sục rửa bị gián đoạn .
-Action: mở chế độ van bypass để nhà sử dụng tạm nước thô tránh hỏng bơm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[GTE-15A01-G] Giải pháp lọc tổng đầu nguồn GE 15A </t>
+    <t>Hoàn thành thay tủ sửa main máy làm mềm , tuy nhiên chưa fix đc lỗi báo muối làm sau xuống thay cả main , màn cùng chủng loại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[WH15A] Giải pháp lọc tổng đầu nguồn GE 15A </t>
   </si>
   <si>
     <t>GTE15A20240006</t>
   </si>
   <si>
     <t>GWT-260013</t>
+  </si>
+  <si>
+    <t>0968256257</t>
   </si>
   <si>
     <t>Chị Ma Tú Lệ</t>
@@ -533,30 +595,30 @@
     <t>Máy báo lỗi E3</t>
   </si>
   <si>
+    <t>GWT-260008</t>
+  </si>
+  <si>
+    <t>Ngoc Chi Bui</t>
+  </si>
+  <si>
+    <t>Máy không vận hành lọc khi tháo/lắp bình nước sau lọc.</t>
+  </si>
+  <si>
+    <t>Máy tiếp tục báo lỗi không vận hành lọc khi tháo bình nước sau lọc ra và lắp vào==&gt;Kỹ thuật thay gioăng cao su==&gt; Máy hoạt đã hoạt động lại</t>
+  </si>
+  <si>
+    <t>GWT-260007</t>
+  </si>
+  <si>
+    <t>Máy không ra nước (máy để bàn)</t>
+  </si>
+  <si>
+    <t>Clean Water Soluition</t>
+  </si>
+  <si>
     <t>Chuyển về trung tâm bảo hành</t>
   </si>
   <si>
-    <t>GWT-260008</t>
-  </si>
-  <si>
-    <t>Ngoc Chi Bui</t>
-  </si>
-  <si>
-    <t>Máy không vận hành lọc khi tháo/lắp bình nước sau lọc.</t>
-  </si>
-  <si>
-    <t>Máy tiếp tục báo lỗi không vận hành lọc khi tháo bình nước sau lọc ra và lắp vào==&gt;Kỹ thuật thay gioăng cao su==&gt; Máy hoạt đã hoạt động lại</t>
-  </si>
-  <si>
-    <t>GWT-260007</t>
-  </si>
-  <si>
-    <t>Máy không ra nước (máy để bàn)</t>
-  </si>
-  <si>
-    <t>Clean Water Soluition</t>
-  </si>
-  <si>
     <t>F00000266V9400030003</t>
   </si>
   <si>
@@ -594,6 +656,9 @@
   </si>
   <si>
     <t>GWT-260004</t>
+  </si>
+  <si>
+    <t>0354822247</t>
   </si>
   <si>
     <t>Lê Xuân Tài</t>
@@ -613,6 +678,9 @@
     <t>GWT-260003</t>
   </si>
   <si>
+    <t>0344566667</t>
+  </si>
+  <si>
     <t>Huỳnh Thị Ánh Nguyên</t>
   </si>
   <si>
@@ -634,6 +702,9 @@
     <t>GWT-260001</t>
   </si>
   <si>
+    <t>0983253544</t>
+  </si>
+  <si>
     <t>Anh Vũ Times City</t>
   </si>
   <si>
@@ -643,6 +714,9 @@
     <t>GWT-250036</t>
   </si>
   <si>
+    <t>0905092015</t>
+  </si>
+  <si>
     <t>Anh An Phạm</t>
   </si>
   <si>
@@ -661,6 +735,9 @@
     <t>GWT-250035</t>
   </si>
   <si>
+    <t>09488782646</t>
+  </si>
+  <si>
     <t>Màn hình cột làm mềm bị đơ không bấm được =&gt; Thay main màn hình</t>
   </si>
   <si>
@@ -688,6 +765,9 @@
     <t>GWT-250033</t>
   </si>
   <si>
+    <t>0979114081</t>
+  </si>
+  <si>
     <t>Anh Tâm</t>
   </si>
   <si>
@@ -706,6 +786,9 @@
     <t>GWT-250032</t>
   </si>
   <si>
+    <t>0966998998</t>
+  </si>
+  <si>
     <t>Đỗ Thị Vân</t>
   </si>
   <si>
@@ -725,6 +808,9 @@
   </si>
   <si>
     <t>Rò rỉ nước</t>
+  </si>
+  <si>
+    <t>0932090929</t>
   </si>
   <si>
     <t>24home (Anh Tovo Nguyen)</t>
@@ -828,6 +914,9 @@
     <t>GWT-250023</t>
   </si>
   <si>
+    <t>0988315201</t>
+  </si>
+  <si>
     <t>A Tuấn</t>
   </si>
   <si>
@@ -837,6 +926,9 @@
     <t>GWT-250022</t>
   </si>
   <si>
+    <t>0908109002</t>
+  </si>
+  <si>
     <t>GWT-250021</t>
   </si>
   <si>
@@ -849,13 +941,16 @@
     <t>Máy CTS10 lỗi chảy nước</t>
   </si>
   <si>
-    <t xml:space="preserve">Team kỹ thuật đã gọi điện không xử lý từ xa được, đã gửi thông tin cho Sơn qua xử lý hẹn 3hpm chiều 20/6/2025 </t>
+    <t xml:space="preserve">Khách báo máy CTS10 lỗi chảy nước. </t>
   </si>
   <si>
     <t>F00000280UC600010036</t>
   </si>
   <si>
     <t>GWT-250020</t>
+  </si>
+  <si>
+    <t>0918231123</t>
   </si>
   <si>
     <t>Trang - Vinhomes Star City Thanh Hoá</t>
@@ -896,6 +991,9 @@
     <t>Hướng dẫn sử dụng</t>
   </si>
   <si>
+    <t>0912489258</t>
+  </si>
+  <si>
     <t>SLP - Trung tâm Giáo dục nghề nghiệp cho người khuyết tật TP.HCM</t>
   </si>
   <si>
@@ -914,6 +1012,9 @@
     <t>Máy kêu to</t>
   </si>
   <si>
+    <t>0792333398</t>
+  </si>
+  <si>
     <t>Nguyễn Trung Hiếu</t>
   </si>
   <si>
@@ -926,6 +1027,9 @@
     <t>GWT-250015</t>
   </si>
   <si>
+    <t>038 9599321</t>
+  </si>
+  <si>
     <t>Hoàng thị thuần</t>
   </si>
   <si>
@@ -938,6 +1042,9 @@
     <t>GWT-250014</t>
   </si>
   <si>
+    <t>0912518070</t>
+  </si>
+  <si>
     <t>Trần Hoàng Hà</t>
   </si>
   <si>
@@ -948,6 +1055,9 @@
   </si>
   <si>
     <t>GWT-250013</t>
+  </si>
+  <si>
+    <t>0943101095</t>
   </si>
   <si>
     <t>F00000214U5M00040001</t>
@@ -975,6 +1085,9 @@
     <t>Màn hình bấm phím không phản hồi (máy để bàn)</t>
   </si>
   <si>
+    <t>0352375127</t>
+  </si>
+  <si>
     <t>Bùi Thu Hà</t>
   </si>
   <si>
@@ -990,6 +1103,9 @@
     <t>GWT-250010</t>
   </si>
   <si>
+    <t>0903458186</t>
+  </si>
+  <si>
     <t>Anh Hiếu, Chị Hannah Olala</t>
   </si>
   <si>
@@ -1000,6 +1116,9 @@
   </si>
   <si>
     <t>GWT-250005</t>
+  </si>
+  <si>
+    <t>0908881816</t>
   </si>
   <si>
     <t>Nguyễn Hùng Cường</t>
@@ -1017,6 +1136,9 @@
   </si>
   <si>
     <t>GWT-250004</t>
+  </si>
+  <si>
+    <t>0934127717</t>
   </si>
   <si>
     <t>Lọc tổng Model GE WH15A01-G không ra nước</t>
@@ -1044,11 +1166,12 @@
     <t>Model GTEC30A01-G không kết nối được Wifi, phím bấm cảm ứng chập chờn</t>
   </si>
   <si>
-    <t xml:space="preserve">Kiểm tra mainboard điều khiển tháo từ khách hàng về. Bấm vẫn không đáp ứng. 
-Thay thế mainboard điều khiển sơ cua từ PO006 vào máy  F00000214U6H00040017 (giữ nguyên modul wifi cũ tháo từ khách hàng về). 
-Test thử hoạt động bình thường. 
-Kết luận: Mainboard điều khiển máy SN F00000214U5M00040001 bị lỗi (chưa rõ nguyên nhân), module wifi vẫn hoạt động bình thường. 
-Đưa vào log báo cáo GWT China để dự trù spareparts dự phòng. </t>
+    <t xml:space="preserve">Model GTEC30A-G không kết nối được wifi, phím bấm cảm ứng chập chờn. 
+Đã liên hệ với GWT China song không có giải pháp khắc phục ngay. 
+Trước mắt để khách hàng sử dụng ngay Team KT GWTVN lấy cả cụm modul wifi + mạch điều khiển từ máy mới để thay thế. (SN:  F00000214U6H00040017)
+Kết quả: 
+Máy sau khi thay linh kiện đã kết nối được wifi, phím bấm cảm ứng vận hành bình thường. 
+Đã vận hành lại thiết bị và bàn giao cho khách hàng. </t>
   </si>
   <si>
     <t>GWT-250002</t>
@@ -1071,6 +1194,9 @@
     <t>GWT-250001</t>
   </si>
   <si>
+    <t>0989646816</t>
+  </si>
+  <si>
     <t>Huyền Đào</t>
   </si>
   <si>
@@ -1086,6 +1212,9 @@
   </si>
   <si>
     <t>GWT-240016</t>
+  </si>
+  <si>
+    <t>0352189629</t>
   </si>
   <si>
     <t>Hoà dương</t>
@@ -1110,13 +1239,18 @@
     <t>Đường nước vào bị bung, vỡ cổng kết nối</t>
   </si>
   <si>
+    <t>0378305084</t>
+  </si>
+  <si>
     <t>Vũ Hương Chi</t>
   </si>
   <si>
     <t>Nước có mùi lạ sau thời gian sử dụng</t>
   </si>
   <si>
-    <t xml:space="preserve">Team KT đã liên hệ khách hàng, xác nhận tình trạng. Đề xuất thu hồi máy về kiểm tra. </t>
+    <t xml:space="preserve">Đã nhận máy và theo dõi. 
+Nước có mùi nhựa nhẹ đã vệ sinh bằng chanh và bình hơi nhiệt 2 tank, kiểm tra chỉ số nước cho ra = 10 ppm lõi sáng và ko có mùi.
+Ngâm nước theo dõi đến 23/12 không có mùi có thể bàn giao lại khách hàng. </t>
   </si>
   <si>
     <t>Phú Thọ (VN)</t>
@@ -1128,6 +1262,9 @@
     <t>GWT-240014</t>
   </si>
   <si>
+    <t>0932227888</t>
+  </si>
+  <si>
     <t>Nguyễn Tuyết Trang</t>
   </si>
   <si>
@@ -1143,6 +1280,9 @@
     <t>GWT-240013</t>
   </si>
   <si>
+    <t>0378495273</t>
+  </si>
+  <si>
     <t>Chị Trang PL 2-18 Vinhome Thanh hoá</t>
   </si>
   <si>
@@ -1158,18 +1298,16 @@
     <t>GWT-240012</t>
   </si>
   <si>
+    <t>0975031993</t>
+  </si>
+  <si>
     <t>Phạm Nhật Hương</t>
   </si>
   <si>
     <t>Máy có mùi lạ sau một thời gian sử dụng</t>
   </si>
   <si>
-    <t>Đã qua nhà khách lấy máy về theo dõi kiểm tra tại Kho phụ
-Đã kiểm tra các chỉ số tds 120/29, pH 6.96 bình thường,  nước có mùi (mùi nhựa) 
-Đã so mùi sau lọc và nước thô đầu vào 
-Action: Mang máy về kho để kiểm tra 3-7 ngày và khách đã đồng ý. 
-             Đã thay bình nước thô kiểm tra vẫn có mùi. 
-             Tiếp tục thay bộ lõi lọc mới: tạm thời hết mùi, chuyển lại cho khách hàng tiếp tục sử dụng và theo dõi</t>
+    <t xml:space="preserve">Khách báo có mùi sau một thời gian sử dụng. </t>
   </si>
   <si>
     <t>F00000156TCK00010150</t>
@@ -1178,13 +1316,16 @@
     <t>GWT-240011</t>
   </si>
   <si>
+    <t>0989499941</t>
+  </si>
+  <si>
     <t>Mrs. Hạnh</t>
   </si>
   <si>
     <t>Chỉ tiêu NO2 cao hơn TCVN1:2018/BYT</t>
   </si>
   <si>
-    <t>Khách hàng phản ánh chỉ tiêu NO2 cao hơn TCVN1:2018/BYT song vẫn thấp hơn QCVN6:1/2010/BYT</t>
+    <t>Đã giải thích cho khách hàng, tuy nhiên khách hàng vẫn không đồng ý. 24home thu hồi máy về để chuyển cho khách hàng khác (thu hồi nội bộ 24 home)</t>
   </si>
   <si>
     <t>F00000157TCB00010016</t>
@@ -1193,6 +1334,9 @@
     <t>GWT-240010</t>
   </si>
   <si>
+    <t>0913275876</t>
+  </si>
+  <si>
     <t>Nguyễn Thị Tuyết Nhung</t>
   </si>
   <si>
@@ -1205,6 +1349,9 @@
     <t>GWT-240009</t>
   </si>
   <si>
+    <t>0963838883</t>
+  </si>
+  <si>
     <t>Chị Tuệ Minh</t>
   </si>
   <si>
@@ -1221,6 +1368,72 @@
   </si>
   <si>
     <t>GWT-240008</t>
+  </si>
+  <si>
+    <t>0989123084</t>
+  </si>
+  <si>
+    <t>Phạm Diễm</t>
+  </si>
+  <si>
+    <t>Máy lọc GN610 nước đầu ra có bụi trắng, khi đưa vào khay nước thô của 50B04 thì phát hiện cặn ở đáy khay nước thô,</t>
+  </si>
+  <si>
+    <t>Đã giải thích về cơ chế giữ khoáng của máy lọc GE. Hẹn sang tuần sau kiểm tra lại, cần thiết sẽ đến tại nhà kiểm tra.</t>
+  </si>
+  <si>
+    <t>F00000157TCB00010062</t>
+  </si>
+  <si>
+    <t>GWT-240007</t>
+  </si>
+  <si>
+    <t>Than phiền về chất lượng nước</t>
+  </si>
+  <si>
+    <t>0919046896</t>
+  </si>
+  <si>
+    <t>Ms Luyến</t>
+  </si>
+  <si>
+    <t>Chưa kết nối được IOT</t>
+  </si>
+  <si>
+    <t>Đã gửi hướng dẫn kết nối IOT</t>
+  </si>
+  <si>
+    <t>TP Hải Phòng (VN)</t>
+  </si>
+  <si>
+    <t>F00000157TCB00010030</t>
+  </si>
+  <si>
+    <t>GWT-240005</t>
+  </si>
+  <si>
+    <t>Đèn báo Wifi không sáng (lọc âm tủ bếp)</t>
+  </si>
+  <si>
+    <t>0982957082</t>
+  </si>
+  <si>
+    <t>Mr Lâm</t>
+  </si>
+  <si>
+    <t>Đề nghị gửi hướng dẫn sử dụng</t>
+  </si>
+  <si>
+    <t>Đã gửi HDSD bản mềm qua nhóm zalo</t>
+  </si>
+  <si>
+    <t>F00000155TCD00010015</t>
+  </si>
+  <si>
+    <t>GWT-240004</t>
+  </si>
+  <si>
+    <t>0902040880</t>
   </si>
 </sst>
 </file>
@@ -1570,13 +1783,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="10" width="30.7109375" customWidth="1"/>
+    <col min="1" max="13" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1607,1594 +1820,1937 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="2">
         <v>46213.64511574074</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="2">
         <v>46210.42917824074</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>30</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="3"/>
+      <c r="M3" s="2">
+        <v>45624.74052083334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="2">
         <v>46151.38996527778</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>40</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" s="3"/>
+      <c r="M4" s="2">
+        <v>46134.63429398148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="2">
         <v>46153.61976851852</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" s="3"/>
+      <c r="M5" s="2">
+        <v>46134.63429398148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="2">
         <v>46198.45753472222</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>51</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L6" s="3"/>
+      <c r="M6" s="2">
+        <v>46157.70372685185</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="2">
         <v>46200.68303240741</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>58</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="M7" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="2">
         <v>46192.41775462963</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>40</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="3"/>
+      <c r="M8" s="2">
+        <v>46134.63429398148</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="2">
         <v>46187.40476851852</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>40</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L9" s="3"/>
+      <c r="M9" s="2">
+        <v>46134.63429398148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="2">
         <v>46181.39494212963</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>40</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="L10" s="3"/>
+      <c r="M10" s="2">
+        <v>46134.63429398148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="2">
         <v>46197.63278935185</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="L11" s="3"/>
+      <c r="M11" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="2">
         <v>46197.62940972222</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="3"/>
+      <c r="M12" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="2">
         <v>46135.72982638889</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>76</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>77</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>40</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="2">
+        <v>46134.63429398148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="2">
         <v>46131.72429398148</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>40</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L14" s="3"/>
+      <c r="M14" s="2">
+        <v>46134.63429398148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="2">
         <v>46194.69159722222</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>103</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="L15" s="3"/>
+      <c r="M15" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="2">
         <v>46194.46665509259</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>40</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="L16" s="3"/>
+      <c r="M16" s="2">
+        <v>46134.63429398148</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="2">
         <v>46197.45369212963</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>58</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="L17" s="3"/>
+      <c r="M17" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="2">
         <v>45993.720625</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>103</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="L18" s="3"/>
+      <c r="M18" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="2">
         <v>46184.49342592592</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="K19" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="L19" s="3"/>
+      <c r="M19" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="2">
         <v>46181.71726851852</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>126</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="L20" s="3"/>
+      <c r="M20" s="2">
+        <v>46134.61287037037</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="2">
         <v>46156.0283449074</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="2">
         <v>46168.02157407408</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L22" s="3"/>
+      <c r="M22" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="2">
         <v>46172.00916666666</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="L23" s="3"/>
+      <c r="M23" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="2">
         <v>46170.01055555556</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="2">
         <v>46157.98174768518</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="2">
         <v>46156.71623842593</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>103</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="L26" s="3"/>
+      <c r="M26" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="2">
         <v>46129.71319444444</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>103</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="L27" s="3"/>
+      <c r="M27" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="2">
         <v>46113.70209490741</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>51</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="L28" s="3"/>
+      <c r="M28" s="2">
+        <v>46157.70372685185</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="2">
         <v>46148.96934027778</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="2">
         <v>46136.9722337963</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="2">
         <v>46134.61505787037</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>40</v>
+      </c>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="2">
+        <v>46134.63429398148</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="2">
         <v>46134.61266203703</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+        <v>40</v>
+      </c>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="2">
+        <v>46134.63429398148</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="2">
         <v>46134.61098379629</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+        <v>40</v>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="2">
+        <v>46134.63429398148</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="2">
         <v>46134.60909722222</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>194</v>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="2">
         <v>46134.53494212963</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>40</v>
+      </c>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="2">
+        <v>46134.63429398148</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="2">
         <v>46134.48369212963</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+        <v>40</v>
+      </c>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="2">
+        <v>46134.63429398148</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="2">
         <v>46134.46587962963</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+        <v>40</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="L37" s="3"/>
+      <c r="M37" s="2">
+        <v>46134.63429398148</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="2">
         <v>46134.46096064815</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>194</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="L38" s="3"/>
+      <c r="M38" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="2">
         <v>46133.57293981482</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>194</v>
+      </c>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="2">
         <v>46109.87024305556</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+        <v>194</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="L40" s="3"/>
+      <c r="M40" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="2">
         <v>46000.325625</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+        <v>103</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="L41" s="3"/>
+      <c r="M41" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="2">
         <v>45964.3087962963</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="L42" s="3"/>
+      <c r="M42" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="2">
         <v>45999.37645833333</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L43" s="3"/>
+      <c r="M43" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="2">
         <v>45995.37390046296</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="L44" s="3"/>
+      <c r="M44" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="2">
         <v>45976.37241898148</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="L45" s="3"/>
+      <c r="M45" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="2">
         <v>45979.41388888889</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
+        <v>259</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="L46" s="3"/>
+      <c r="M46" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="2">
         <v>45938.44902777778</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>232</v>
+        <v>261</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
+        <v>259</v>
+      </c>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="2">
         <v>45925.32296296296</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="3" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>238</v>
+        <v>267</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
+        <v>259</v>
+      </c>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="2">
         <v>45915.34902777777</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
+        <v>259</v>
+      </c>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="2">
         <v>45903.37373842593</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
+        <v>103</v>
+      </c>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="2">
         <v>45845.74392361111</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>249</v>
+        <v>278</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>250</v>
+        <v>279</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
+        <v>280</v>
+      </c>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="2">
         <v>45845.7427662037</v>
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3" t="s">
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>253</v>
+        <v>282</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>254</v>
+        <v>283</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
+        <v>259</v>
+      </c>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="2">
         <v>45845.74145833333</v>
       </c>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3" t="s">
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>256</v>
+        <v>285</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>257</v>
+        <v>286</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
+        <v>287</v>
+      </c>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="2">
         <v>45845.72974537037</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>261</v>
+        <v>290</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
+        <v>259</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="L54" s="3"/>
+      <c r="M54" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="2">
         <v>45840.74769675926</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
+        <v>103</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="L55" s="3"/>
+      <c r="M55" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
       <c r="A56" s="2">
         <v>45833.50961805556</v>
       </c>
@@ -3205,777 +3761,1070 @@
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10">
+        <v>300</v>
+      </c>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
       <c r="A57" s="2">
         <v>45827.49487268519</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
+        <v>259</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="L57" s="3"/>
+      <c r="M57" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
       <c r="A58" s="2">
         <v>45758.68524305556</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="3" t="s">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
+        <v>287</v>
+      </c>
+      <c r="K58" s="3"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13">
       <c r="A59" s="2">
         <v>45744.6565162037</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>256</v>
+        <v>285</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
+        <v>287</v>
+      </c>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
       <c r="A60" s="2">
         <v>45736.48413194445</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>281</v>
+        <v>313</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>282</v>
+        <v>314</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>283</v>
+        <v>315</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>285</v>
+        <v>317</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10">
+        <v>318</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="L60" s="3"/>
+      <c r="M60" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
       <c r="A61" s="2">
         <v>45730.67275462963</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>287</v>
+        <v>320</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3" t="s">
-        <v>288</v>
+        <v>321</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>289</v>
+        <v>322</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>290</v>
+        <v>323</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>291</v>
+        <v>324</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
+        <v>325</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="L61" s="3"/>
+      <c r="M61" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13">
       <c r="A62" s="2">
         <v>45782.66892361111</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>293</v>
+        <v>327</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3" t="s">
-        <v>294</v>
+        <v>328</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>296</v>
+        <v>330</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10">
+        <v>287</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="L62" s="3"/>
+      <c r="M62" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
       <c r="A63" s="2">
         <v>45729.59361111111</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>297</v>
+        <v>332</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3" t="s">
-        <v>298</v>
+        <v>333</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>299</v>
+        <v>334</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="L63" s="3"/>
+      <c r="M63" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13">
       <c r="A64" s="2">
         <v>45721.52947916667</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>303</v>
+        <v>339</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>304</v>
+        <v>340</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="L64" s="3"/>
+      <c r="M64" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13">
       <c r="A65" s="2">
         <v>45721.52597222223</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
-        <v>305</v>
+        <v>342</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>306</v>
+        <v>343</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="L65" s="3"/>
+      <c r="M65" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13">
       <c r="A66" s="2">
         <v>45721.48268518518</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>307</v>
+        <v>344</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>308</v>
+        <v>345</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>310</v>
+        <v>347</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
+        <v>349</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="L66" s="3"/>
+      <c r="M66" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13">
       <c r="A67" s="2">
         <v>45719.75399305556</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>314</v>
+        <v>352</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>315</v>
+        <v>353</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>316</v>
+        <v>354</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="L67" s="3"/>
+      <c r="M67" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13">
       <c r="A68" s="2">
         <v>45714.42311342592</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="C68" s="3"/>
       <c r="D68" s="3" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>321</v>
+        <v>360</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
+        <v>349</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="L68" s="3"/>
+      <c r="M68" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13">
       <c r="A69" s="2">
         <v>45682.73614583333</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>323</v>
+        <v>363</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>324</v>
+        <v>364</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>325</v>
+        <v>365</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>326</v>
+        <v>366</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
+        <v>194</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="L69" s="3"/>
+      <c r="M69" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13">
       <c r="A70" s="2">
         <v>45682.67493055556</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>329</v>
+        <v>370</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>330</v>
+        <v>371</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>331</v>
+        <v>372</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="L70" s="3"/>
+      <c r="M70" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13">
       <c r="A71" s="2">
         <v>45693.70677083333</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>332</v>
+        <v>373</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>333</v>
+        <v>374</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>305</v>
+        <v>342</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>334</v>
+        <v>375</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="L71" s="3"/>
+      <c r="M71" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13">
       <c r="A72" s="2">
         <v>45671.46908564815</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>335</v>
+        <v>376</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>336</v>
+        <v>377</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>337</v>
+        <v>378</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>261</v>
+        <v>290</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
+        <v>259</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="L72" s="3"/>
+      <c r="M72" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13">
       <c r="A73" s="2">
         <v>45521.58040509259</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>341</v>
+        <v>383</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>343</v>
+        <v>385</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>253</v>
+        <v>282</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>344</v>
+        <v>386</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10">
+        <v>259</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="L73" s="3"/>
+      <c r="M73" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13">
       <c r="A74" s="2">
         <v>45649.77418981482</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>345</v>
+        <v>388</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>346</v>
+        <v>389</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>347</v>
+        <v>390</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>261</v>
+        <v>290</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>349</v>
+        <v>392</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10">
+        <v>393</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="L74" s="3"/>
+      <c r="M74" s="2">
+        <v>45650.6084375</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
       <c r="A75" s="2">
         <v>45649.47976851852</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>351</v>
+        <v>395</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>352</v>
+        <v>396</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>353</v>
+        <v>397</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>354</v>
+        <v>398</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>355</v>
+        <v>399</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>356</v>
+        <v>400</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10">
+        <v>30</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="L75" s="3"/>
+      <c r="M75" s="2">
+        <v>45624.74052083334</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13">
       <c r="A76" s="2">
         <v>45638.70994212963</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>357</v>
+        <v>402</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>358</v>
+        <v>403</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>359</v>
+        <v>404</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>329</v>
+        <v>370</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>360</v>
+        <v>405</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>361</v>
+        <v>406</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10">
+        <v>21</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="L76" s="3"/>
+      <c r="M76" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
       <c r="A77" s="2">
         <v>45625.45730324074</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>362</v>
+        <v>408</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>352</v>
+        <v>396</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>363</v>
+        <v>409</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>364</v>
+        <v>410</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>365</v>
+        <v>411</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>366</v>
+        <v>412</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10">
+        <v>287</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="L77" s="3"/>
+      <c r="M77" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13">
       <c r="A78" s="2">
         <v>45624.74232638889</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>367</v>
+        <v>414</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>368</v>
+        <v>415</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>369</v>
+        <v>416</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>370</v>
+        <v>417</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>371</v>
+        <v>418</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10">
+        <v>287</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="L78" s="3"/>
+      <c r="M78" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13">
       <c r="A79" s="2">
         <v>45439.51983796297</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>372</v>
+        <v>420</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>373</v>
+        <v>421</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>261</v>
+        <v>290</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>375</v>
+        <v>423</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>376</v>
+        <v>424</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10">
+        <v>300</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="L79" s="3"/>
+      <c r="M79" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13">
       <c r="A80" s="2">
         <v>45539.51461805555</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>377</v>
+        <v>426</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>378</v>
+        <v>427</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>378</v>
+        <v>427</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>261</v>
+        <v>290</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>379</v>
+        <v>428</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>380</v>
+        <v>429</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10">
+        <v>300</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="L80" s="3"/>
+      <c r="M80" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13">
       <c r="A81" s="2">
         <v>45531.59709490741</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>381</v>
+        <v>431</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>382</v>
+        <v>432</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>383</v>
+        <v>433</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>384</v>
+        <v>434</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>385</v>
+        <v>435</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>386</v>
+        <v>436</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>231</v>
+        <v>259</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="L81" s="3"/>
+      <c r="M81" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13">
+      <c r="A82" s="2">
+        <v>45527.71017361111</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="L82" s="3"/>
+      <c r="M82" s="2">
+        <v>45527.71069444445</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13">
+      <c r="A83" s="2">
+        <v>45485.79615740741</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="L83" s="3"/>
+      <c r="M83" s="2">
+        <v>45477.65123842593</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13">
+      <c r="A84" s="2">
+        <v>45481.58848379629</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="L84" s="3"/>
+      <c r="M84" s="2">
+        <v>45477.65123842593</v>
       </c>
     </row>
   </sheetData>
